--- a/Reports/FIO/CertificateToCourt/Certificate.xlsx
+++ b/Reports/FIO/CertificateToCourt/Certificate.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20827"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenServer\domains\REPORTS-test\Reports\FIO\CertificateToCourt\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7969C60-DDB9-4F1F-B8F6-2859EB05AF96}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="45" windowWidth="28560" windowHeight="12600"/>
+    <workbookView xWindow="120" yWindow="45" windowWidth="28560" windowHeight="12600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -51,9 +57,6 @@
     <t>СПРАВКА</t>
   </si>
   <si>
-    <t>в том, что он (она) действительно зарегистрирован(а) в  г. Белово</t>
-  </si>
-  <si>
     <t>Совместно с ним зарегистрированы:</t>
   </si>
   <si>
@@ -94,13 +97,16 @@
   </si>
   <si>
     <t>$this-&gt;H['AccrualsForYear']." _________________________ ".$this-&gt;H['Signatory']</t>
+  </si>
+  <si>
+    <t>"в том, что он (она) действительно зарегистрирован(а) в  ".$this-&gt;H['pref_region']." " .$this-&gt;H['name_region']</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -275,6 +281,14 @@
       <color rgb="FFFFFFCC"/>
     </mruColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -321,7 +335,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -353,9 +367,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -387,6 +419,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -562,12 +612,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
     <col min="4" max="4" width="5.7109375" customWidth="1"/>
@@ -583,10 +633,10 @@
     <col min="16" max="18" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C1" s="26"/>
       <c r="D1" s="26"/>
@@ -611,62 +661,62 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="26"/>
       <c r="C2" s="26"/>
       <c r="D2" s="26"/>
       <c r="E2" s="6"/>
       <c r="F2" s="21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G2" s="22"/>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" s="26"/>
       <c r="C3" s="26"/>
       <c r="D3" s="26"/>
       <c r="E3" s="6"/>
       <c r="F3" s="17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3" s="24"/>
     </row>
-    <row r="4" spans="1:18" ht="30" customHeight="1">
+    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
       <c r="E4" s="6"/>
       <c r="F4" s="17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G4" s="17"/>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="26"/>
       <c r="C5" s="26"/>
       <c r="D5" s="26"/>
       <c r="E5" s="6"/>
       <c r="F5" s="18" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G5" s="18"/>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="26"/>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
       <c r="E6" s="6"/>
       <c r="F6" s="19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6" s="23"/>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
       <c r="B7" s="26"/>
       <c r="C7" s="26"/>
@@ -675,7 +725,7 @@
       <c r="F7" s="19"/>
       <c r="G7" s="19"/>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="26"/>
       <c r="C8" s="26"/>
@@ -684,7 +734,7 @@
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -693,9 +743,9 @@
       <c r="F9" s="10"/>
       <c r="G9" s="10"/>
     </row>
-    <row r="10" spans="1:18" ht="15" customHeight="1">
+    <row r="10" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="6"/>
@@ -711,7 +761,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="3.75" customHeight="1">
+    <row r="11" spans="1:18" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="12"/>
@@ -723,22 +773,22 @@
         <v>3</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K11" s="2">
         <v>1</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
     </row>
-    <row r="12" spans="1:18" ht="15" customHeight="1">
+    <row r="12" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="9"/>
       <c r="C12" s="20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D12" s="20"/>
       <c r="E12" s="20"/>
@@ -754,16 +804,16 @@
         <v>3</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
     </row>
-    <row r="13" spans="1:18" ht="15" customHeight="1">
+    <row r="13" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
       <c r="B13" s="9"/>
       <c r="C13" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
@@ -775,11 +825,11 @@
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
     </row>
-    <row r="14" spans="1:18" ht="15" customHeight="1">
+    <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D14" s="15"/>
       <c r="E14" s="15"/>
@@ -800,7 +850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="15" customHeight="1">
+    <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12"/>
       <c r="B15" s="12"/>
       <c r="C15" s="11"/>
@@ -815,11 +865,11 @@
         <v>6</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O15" s="2"/>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="9"/>
       <c r="C16" s="6"/>
@@ -840,9 +890,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="6"/>
@@ -851,7 +901,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="9"/>
       <c r="C18" s="6"/>
@@ -860,9 +910,9 @@
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" s="9"/>
       <c r="C19" s="6"/>
@@ -871,7 +921,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="9"/>
       <c r="C20" s="6"/>
@@ -880,7 +930,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -889,7 +939,7 @@
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="M25" s="2" t="s">
         <v>6</v>
       </c>
@@ -922,18 +972,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Reports/FIO/CertificateToCourt/Certificate.xlsx
+++ b/Reports/FIO/CertificateToCourt/Certificate.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenServer\domains\REPORTS-test\Reports\FIO\CertificateToCourt\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenServer\domains\REPORTS\Reports\FIO\CertificateToCourt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7969C60-DDB9-4F1F-B8F6-2859EB05AF96}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96745205-E010-4B86-BCF4-1559BFCCE62E}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="45" windowWidth="28560" windowHeight="12600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -243,9 +243,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -269,6 +266,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -635,11 +635,11 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
       <c r="E1" s="6"/>
       <c r="F1" s="16" t="s">
         <v>9</v>
@@ -663,73 +663,73 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="6"/>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="22"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
       <c r="E3" s="6"/>
       <c r="F3" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="24"/>
+      <c r="G3" s="23"/>
     </row>
     <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
       <c r="E4" s="6"/>
       <c r="F4" s="17" t="s">
         <v>16</v>
       </c>
       <c r="G4" s="17"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
       <c r="E5" s="6"/>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="18"/>
+      <c r="G5" s="26"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
       <c r="E6" s="6"/>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="23"/>
+      <c r="G6" s="22"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
       <c r="E7" s="6"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
       <c r="E8" s="9"/>
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
@@ -787,13 +787,13 @@
     <row r="12" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="9"/>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
       <c r="I12" s="3" t="s">
         <v>1</v>
       </c>
